--- a/StructureDefinition-Presentationsformat.xlsx
+++ b/StructureDefinition-Presentationsformat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Presentationsformat.xlsx
+++ b/StructureDefinition-Presentationsformat.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Presentationsformat).</t>
+    <t>Typ av filformat för svaret. 
+[Så står det nu i informationsmodellen, klassen Svar, attributet "presentationsformat". Detta behöver knappast finnas med i begreppsmodellen.]
+Dokument som innehåller den visuella presentationen av laboratoriesvaret.  
+Men jfr projektet e-remiss, där finns bilaga:  
+Dokument som kompletterar ett annat dokument och är avsett att användas tillsammans med detta.   
+Exempelvis utdrag ur patientjournal, en bild eller liknande som biläggs remissen, eller remissvaret.  
+Är presentation något annat än bilaga?</t>
   </si>
   <si>
     <t>Purpose</t>
